--- a/ProductBacklog_group68.xlsx
+++ b/ProductBacklog_group68.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
   <si>
     <t>1. The system provides role options for TA, MO and Admin.
 2. The user can enter email(or student id) and password to log in.
-3. The system validates whether the email and password are correct.
+3. The system validates whether the email(or student id) and password are correct.
 4. If the login is successful, the user is redirected to the correct dashboard according to the selected role.
 5. If the login fails, the system displays an error message.
 6. The system does not allow access to another role’s pages without permission.</t>
@@ -142,6 +142,9 @@
 So that I can quickly understand my current status in the system.</t>
   </si>
   <si>
+    <t>Should have</t>
+  </si>
+  <si>
     <t>1. The dashboard shows TA basic profile information.
 2. The dashboard shows CV status.
 3. The dashboard shows the number of applications by status, for example pending, accepted or rejected.
@@ -423,9 +426,6 @@
     <t>As an administrator
 I want to view the overall workload of TAs across applications and assignments
 So that I can monitor fairness and avoid over-allocation.</t>
-  </si>
-  <si>
-    <t>Should have</t>
   </si>
   <si>
     <t>1. The admin can view a list of TAs with their current number of applications and assignments.
@@ -1153,11 +1153,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1524,769 +1521,732 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.16666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.6666666666667" style="4" customWidth="1"/>
-    <col min="3" max="3" width="62" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.8888888888889" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.4444444444444" style="4" customWidth="1"/>
-    <col min="6" max="6" width="61.5555555555556" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.8333333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.1666666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.8333333333333" style="4" customWidth="1"/>
-    <col min="10" max="10" width="26.3333333333333" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.83333333333333" style="2"/>
+    <col min="1" max="1" width="9.16666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.6666666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="62" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.8888888888889" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.4444444444444" style="3" customWidth="1"/>
+    <col min="6" max="6" width="61.5555555555556" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.1666666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.8333333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="26.3333333333333" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.83333333333333" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:47">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="28.8" spans="1:10">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="165" customHeight="1" spans="1:47">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="165" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>3</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>46097</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>46103</v>
       </c>
     </row>
-    <row r="3" ht="201.6" spans="1:47">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="201.6" spans="1:10">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>46097</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>46103</v>
       </c>
     </row>
-    <row r="4" ht="158.4" spans="1:47">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="158.4" spans="1:10">
+      <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>46097</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>46103</v>
       </c>
     </row>
-    <row r="5" ht="115.2" spans="1:47">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="115.2" spans="1:10">
+      <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46104</v>
+      </c>
+      <c r="J5" s="6">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="6" ht="158.4" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46104</v>
+      </c>
+      <c r="J6" s="6">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="72" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="4">
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46104</v>
+      </c>
+      <c r="J7" s="6">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="129.6" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="3">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="H8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="6">
         <v>46104</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J8" s="6">
         <v>46110</v>
       </c>
     </row>
-    <row r="6" ht="158.4" spans="1:47">
-      <c r="A6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="4" t="s">
+    <row r="9" s="1" customFormat="1" ht="100.8" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46104</v>
+      </c>
+      <c r="J9" s="6">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="10" ht="172.8" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="6">
         <v>46104</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J10" s="6">
         <v>46110</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="72" spans="1:47">
-      <c r="A7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="4" t="s">
+    <row r="11" s="1" customFormat="1" ht="273.6" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46111</v>
+      </c>
+      <c r="J11" s="6">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="12" ht="144" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="3">
         <v>3</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J7" s="7">
-        <v>46110</v>
+      <c r="H12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46111</v>
+      </c>
+      <c r="J12" s="6">
+        <v>46117</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="129.6" spans="1:47">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="4" t="s">
+    <row r="13" ht="244.8" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
         <v>5</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J8" s="7">
-        <v>46110</v>
+      <c r="H13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="6">
+        <v>46118</v>
+      </c>
+      <c r="J13" s="6">
+        <v>46124</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="100.8" spans="1:47">
-      <c r="A9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
+    <row r="14" ht="115.2" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="3">
         <v>3</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J9" s="7">
-        <v>46110</v>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
+      <c r="H14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46118</v>
+      </c>
+      <c r="J14" s="6">
+        <v>46124</v>
+      </c>
     </row>
-    <row r="10" ht="172.8" spans="1:47">
-      <c r="A10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="4" t="s">
+    <row r="15" ht="187.2" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46145</v>
+      </c>
+      <c r="J15" s="6">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="16" ht="158.4" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="3">
         <v>5</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J10" s="7">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="273.6" spans="1:47">
-      <c r="A11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="4">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="4">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="7">
-        <v>46111</v>
-      </c>
-      <c r="J11" s="7">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="12" ht="144" spans="1:47">
-      <c r="A12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="4">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="4">
-        <v>3</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="7">
-        <v>46111</v>
-      </c>
-      <c r="J12" s="7">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="13" ht="244.8" spans="1:47">
-      <c r="A13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="4">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="4">
-        <v>5</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="7">
-        <v>46118</v>
-      </c>
-      <c r="J13" s="7">
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="14" ht="115.2" spans="1:47">
-      <c r="A14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="4">
-        <v>3</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="7">
-        <v>46118</v>
-      </c>
-      <c r="J14" s="7">
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="15" ht="187.2" spans="1:47">
-      <c r="A15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="4">
-        <v>3</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="4">
-        <v>3</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="7">
+      <c r="H16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="6">
         <v>46145</v>
       </c>
-      <c r="J15" s="7">
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="16" ht="158.4" spans="1:47">
-      <c r="A16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="4">
-        <v>5</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="7">
-        <v>46145</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="J16" s="6">
         <v>46152</v>
       </c>
     </row>
     <row r="17" ht="158.4" spans="1:10">
-      <c r="A17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>3</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="F17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="3">
         <v>8</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="7">
+      <c r="H17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="6">
         <v>46145</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="6">
         <v>46152</v>
       </c>
     </row>
     <row r="18" ht="115.2" spans="1:10">
-      <c r="A18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="4">
+      <c r="D18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="3">
         <v>4</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>5</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <v>46153</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="6">
         <v>46159</v>
       </c>
     </row>
     <row r="19" ht="268" customHeight="1" spans="1:10">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="3">
         <v>4</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>3</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <v>46153</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>46159</v>
       </c>
     </row>
     <row r="20" ht="144" spans="1:10">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3">
         <v>4</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>3</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <v>46153</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="6">
         <v>46169</v>
       </c>
     </row>
     <row r="21" ht="173" customHeight="1" spans="1:10">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>4</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>5</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="6">
         <v>46160</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="6">
         <v>46166</v>
       </c>
     </row>
     <row r="22" ht="230.4" spans="1:10">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>4</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="3">
         <v>3</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="6">
         <v>46160</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="6">
         <v>46166</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10 D15 D1:D9 D11:D14 D16:D18 D19:D22 D24:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D22 D24:D1048576">
       <formula1>"Must have,Should have,Could have"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10 G15 G1:G9 G11:G14 G16:G18 G19:G22 G24:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G22 G24:G1048576">
       <formula1>"1,2,3,5,8,13"</formula1>
     </dataValidation>
   </dataValidations>
